--- a/artifacts/advanced-navigator/advanced.xlsx
+++ b/artifacts/advanced-navigator/advanced.xlsx
@@ -88,7 +88,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -110,6 +110,34 @@
         <color rgb="0041484D"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="0041484D"/>
+      </left>
+      <right style="medium">
+        <color rgb="004DAAFC"/>
+      </right>
+      <top style="thin">
+        <color rgb="0041484D"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00FFCC00"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0041484D"/>
+      </left>
+      <right style="thin">
+        <color rgb="0041484D"/>
+      </right>
+      <top style="thin">
+        <color rgb="0041484D"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00FFCC00"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -122,13 +150,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -231,9 +259,11 @@
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
         <t>T1000  Alpha
+Alpha
 Score: 8.5
 Selected: True
 Enabled: True
+Annotation indicators: #ffcc00, #4daafc
 Parent note
 Owner: Research team
 Updated case: https://example.org/case</t>
@@ -241,25 +271,30 @@
     </comment>
     <comment ref="A5" authorId="0" shapeId="0">
       <text>
-        <t>&gt; T1000.001  Child
+        <t>T1000.001  Child
+&gt; Child
 Score: 2
 Selected: True
 Enabled: True
+Annotation indicators: #ffcc00
 Scoped child note</t>
       </text>
     </comment>
     <comment ref="A6" authorId="0" shapeId="0">
       <text>
         <t>T1002  Legacy
+Legacy
 Score: 4
 Selected: True
 Enabled: True
+Annotation indicators: #ffcc00
 Legacy observation</t>
       </text>
     </comment>
     <comment ref="A7" authorId="0" shapeId="0">
       <text>
         <t>T1001  Beta
+Beta
 Selected: True
 Enabled: True</t>
       </text>
@@ -587,7 +622,7 @@
     <row r="4" ht="50" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>T1000  Alpha
+          <t>Alpha
 Score: 8.5</t>
         </is>
       </c>
@@ -595,7 +630,7 @@
     <row r="5" ht="50" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>&gt; T1000.001  Child
+          <t>&gt; Child
 Score: 2</t>
         </is>
       </c>
@@ -603,7 +638,7 @@
     <row r="6" ht="50" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>T1002  Legacy
+          <t>Legacy
 Score: 4</t>
         </is>
       </c>
@@ -611,7 +646,7 @@
     <row r="7" ht="35" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>T1001  Beta</t>
+          <t>Beta</t>
         </is>
       </c>
     </row>
